--- a/public/format-import.xlsx
+++ b/public/format-import.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
   <si>
     <t xml:space="preserve">no</t>
   </si>
@@ -41,6 +41,21 @@
   </si>
   <si>
     <t xml:space="preserve">e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">val_a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">val_b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">val_c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">val_d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">val_e</t>
   </si>
   <si>
     <t xml:space="preserve">kc</t>
@@ -192,8 +207,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:M4"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -217,8 +232,23 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="0" t="s">
         <v>7</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -226,24 +256,39 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="L2" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -252,24 +297,39 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="E3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="G3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J3" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -278,24 +338,39 @@
         <v>3</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J4" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="M4" s="0" t="s">
         <v>5</v>
       </c>
     </row>
